--- a/data/obx_xlsx/PLT.OL.xlsx
+++ b/data/obx_xlsx/PLT.OL.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="307">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -618,28 +618,31 @@
     <t>Total equity</t>
   </si>
   <si>
+    <t xml:space="preserve">Interest-bearing loans and borrowings (Do not use) </t>
+  </si>
+  <si>
+    <t>Lease liabilities</t>
+  </si>
+  <si>
+    <t>Total non-current liabilities</t>
+  </si>
+  <si>
+    <t>Trade and other payables</t>
+  </si>
+  <si>
+    <t>Trade payables</t>
+  </si>
+  <si>
+    <t>Other payables and accruals</t>
+  </si>
+  <si>
+    <t>Accrued Expenses</t>
+  </si>
+  <si>
+    <t>Trade and other payables - Balancing value</t>
+  </si>
+  <si>
     <t>Interest-bearing loans and borrowings</t>
-  </si>
-  <si>
-    <t>Lease liabilities</t>
-  </si>
-  <si>
-    <t>Total non-current liabilities</t>
-  </si>
-  <si>
-    <t>Trade and other payables</t>
-  </si>
-  <si>
-    <t>Trade payables</t>
-  </si>
-  <si>
-    <t>Other payables and accruals</t>
-  </si>
-  <si>
-    <t>Accrued Expenses</t>
-  </si>
-  <si>
-    <t>Trade and other payables - Balancing value</t>
   </si>
   <si>
     <t>Current lease liabilities</t>
@@ -1062,7 +1065,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1143,6 +1146,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="3" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -7561,7 +7567,7 @@
       </c>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="13" t="s">
+      <c r="A65" s="27" t="s">
         <v>199</v>
       </c>
       <c r="B65" s="14">
@@ -7794,7 +7800,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="13" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="B73" s="14">
         <v>0.06</v>
@@ -7826,7 +7832,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="13" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B74" s="14">
         <v>0.78</v>
@@ -7856,7 +7862,7 @@
     </row>
     <row r="75" ht="15.0" customHeight="1">
       <c r="A75" s="13" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B75" s="15"/>
       <c r="C75" s="15"/>
@@ -7884,7 +7890,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="13" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B76" s="14">
         <v>1.0</v>
@@ -7922,7 +7928,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="13" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B77" s="15"/>
       <c r="C77" s="15"/>
@@ -7946,7 +7952,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="17" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B78" s="18">
         <v>23.57</v>
@@ -7984,7 +7990,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="13" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B79" s="15"/>
       <c r="C79" s="15"/>
@@ -8004,7 +8010,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="17" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B80" s="18">
         <v>33.56</v>
@@ -8042,7 +8048,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="13" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B81" s="15"/>
       <c r="C81" s="15"/>
@@ -8060,7 +8066,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="17" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B82" s="21">
         <v>372.78</v>
@@ -8098,7 +8104,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="13" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B83" s="15">
         <v>0.0</v>
@@ -8136,7 +8142,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B84" s="26">
         <v>212.77</v>
@@ -8174,7 +8180,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="13" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B85" s="26">
         <v>212.77</v>
@@ -8212,7 +8218,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="13" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B86" s="15"/>
       <c r="C86" s="14">
@@ -8230,7 +8236,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="13" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B87" s="15"/>
       <c r="C87" s="14">
@@ -8248,7 +8254,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="13" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B88" s="15"/>
       <c r="C88" s="14">
@@ -8266,7 +8272,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="13" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B89" s="15"/>
       <c r="C89" s="14">
@@ -8284,7 +8290,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B90" s="15"/>
       <c r="C90" s="15">
@@ -8302,7 +8308,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="13" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B91" s="15"/>
       <c r="C91" s="14">
@@ -8330,7 +8336,7 @@
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="13" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B92" s="15"/>
       <c r="C92" s="14">
@@ -8358,7 +8364,7 @@
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="13" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B93" s="15"/>
       <c r="C93" s="14">
@@ -8386,7 +8392,7 @@
     </row>
     <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="13" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B94" s="15"/>
       <c r="C94" s="14">
@@ -8404,7 +8410,7 @@
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="13" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B95" s="15"/>
       <c r="C95" s="16">
@@ -8424,7 +8430,7 @@
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="13" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B96" s="26">
         <v>212.77</v>
@@ -8462,7 +8468,7 @@
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="13" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B97" s="15">
         <v>0.0</v>
@@ -8500,7 +8506,7 @@
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="13" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B98" s="26">
         <v>212.77</v>
@@ -8538,7 +8544,7 @@
     </row>
     <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="13" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B99" s="14">
         <v>1.0</v>
@@ -8576,7 +8582,7 @@
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="13" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B100" s="15"/>
       <c r="C100" s="14">
@@ -8604,7 +8610,7 @@
     </row>
     <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="13" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B101" s="15"/>
       <c r="C101" s="26">
@@ -9551,7 +9557,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -9794,42 +9800,42 @@
         <v>33</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -9883,7 +9889,7 @@
     </row>
     <row r="19" ht="15.0" customHeight="1">
       <c r="A19" s="13" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B19" s="24">
         <v>-118.05</v>
@@ -9921,7 +9927,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="13" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B20" s="14">
         <v>3.35</v>
@@ -9959,7 +9965,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="13" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B21" s="14">
         <v>7.28</v>
@@ -9995,7 +10001,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="13" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B22" s="20">
         <v>-9.1</v>
@@ -10023,7 +10029,7 @@
     </row>
     <row r="23" ht="15.0" customHeight="1">
       <c r="A23" s="13" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B23" s="14">
         <v>15.23</v>
@@ -10061,7 +10067,7 @@
     </row>
     <row r="24" ht="15.0" customHeight="1">
       <c r="A24" s="13" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B24" s="20">
         <v>-0.01</v>
@@ -10083,7 +10089,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="13" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B25" s="20">
         <v>-0.23</v>
@@ -10121,7 +10127,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="13" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B26" s="20">
         <v>-0.12</v>
@@ -10159,7 +10165,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="13" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B27" s="20">
         <v>-8.38</v>
@@ -10197,7 +10203,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B28" s="14">
         <v>8.92</v>
@@ -10231,7 +10237,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="13" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B29" s="14">
         <v>7.61</v>
@@ -10269,7 +10275,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="13" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B30" s="20">
         <v>-6.68</v>
@@ -10307,7 +10313,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="13" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B31" s="14">
         <v>10.51</v>
@@ -10345,7 +10351,7 @@
     </row>
     <row r="32" ht="15.0" customHeight="1">
       <c r="A32" s="13" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B32" s="20">
         <v>-0.96</v>
@@ -10381,7 +10387,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="13" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B33" s="20">
         <v>-0.21</v>
@@ -10413,7 +10419,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="13" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B34" s="15"/>
       <c r="C34" s="15"/>
@@ -10431,7 +10437,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="13" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B35" s="15"/>
       <c r="C35" s="15"/>
@@ -10449,7 +10455,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B36" s="15"/>
       <c r="C36" s="16">
@@ -10481,7 +10487,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="17" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B37" s="23">
         <v>-90.85</v>
@@ -10519,7 +10525,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="13" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B38" s="14">
         <v>0.05</v>
@@ -10541,7 +10547,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="13" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B39" s="20">
         <v>-1.68</v>
@@ -10579,7 +10585,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="13" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B40" s="15"/>
       <c r="C40" s="15"/>
@@ -10607,7 +10613,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="13" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B41" s="15"/>
       <c r="C41" s="15"/>
@@ -10635,7 +10641,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="13" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B42" s="15"/>
       <c r="C42" s="15"/>
@@ -10655,7 +10661,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="17" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B43" s="23">
         <v>-1.64</v>
@@ -10693,7 +10699,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="13" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B44" s="14">
         <v>0.94</v>
@@ -10721,7 +10727,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="13" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B45" s="26">
         <v>222.91</v>
@@ -10759,7 +10765,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="13" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B46" s="20">
         <v>-13.38</v>
@@ -10797,7 +10803,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="13" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B47" s="20">
         <v>-0.71</v>
@@ -10827,7 +10833,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="13" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B48" s="20">
         <v>-0.06</v>
@@ -10859,7 +10865,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B49" s="15">
         <v>0.0</v>
@@ -10879,7 +10885,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="13" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B50" s="15"/>
       <c r="C50" s="15"/>
@@ -10897,7 +10903,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="17" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B51" s="21">
         <v>209.7</v>
@@ -10935,7 +10941,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="13" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B52" s="26">
         <v>166.75</v>
@@ -10973,7 +10979,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="13" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B53" s="26">
         <v>283.98</v>
@@ -11011,7 +11017,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="13" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B54" s="14">
         <v>0.01</v>
@@ -11049,7 +11055,7 @@
     </row>
     <row r="55" ht="15.0" customHeight="1">
       <c r="A55" s="13" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B55" s="26">
         <v>117.22</v>
@@ -11087,7 +11093,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="17" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B56" s="21">
         <v>117.23</v>
@@ -12089,7 +12095,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -12351,7 +12357,7 @@
     </row>
     <row r="17">
       <c r="A17" s="11" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B17" s="6"/>
       <c r="C17" s="6"/>
@@ -12400,675 +12406,675 @@
       </c>
     </row>
     <row r="19" ht="15.0" customHeight="1">
-      <c r="A19" s="27" t="s">
-        <v>277</v>
-      </c>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28"/>
-      <c r="K19" s="28"/>
+      <c r="A19" s="28" t="s">
+        <v>278</v>
+      </c>
+      <c r="B19" s="29"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="29"/>
+      <c r="E19" s="29"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="29"/>
+      <c r="H19" s="29"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="29"/>
+      <c r="K19" s="29"/>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="29" t="s">
-        <v>277</v>
-      </c>
-      <c r="B20" s="30">
+      <c r="A20" s="30" t="s">
+        <v>278</v>
+      </c>
+      <c r="B20" s="31">
         <v>466.02</v>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="31">
         <v>1309.77</v>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="31">
         <v>882.26</v>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="31">
         <v>1784.29</v>
       </c>
-      <c r="F20" s="30">
+      <c r="F20" s="31">
         <v>686.62</v>
       </c>
-      <c r="G20" s="30">
+      <c r="G20" s="31">
         <v>247.86</v>
       </c>
-      <c r="H20" s="30">
+      <c r="H20" s="31">
         <v>124.79</v>
       </c>
-      <c r="I20" s="31"/>
-      <c r="J20" s="31"/>
-      <c r="K20" s="31"/>
+      <c r="I20" s="32"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="32"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="29" t="s">
-        <v>278</v>
-      </c>
-      <c r="B21" s="30">
+      <c r="A21" s="30" t="s">
+        <v>279</v>
+      </c>
+      <c r="B21" s="31">
         <v>1025.79</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="31">
         <v>982.16</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="31">
         <v>745.17</v>
       </c>
-      <c r="E21" s="31"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="31"/>
-      <c r="J21" s="31"/>
-      <c r="K21" s="31"/>
+      <c r="E21" s="32"/>
+      <c r="F21" s="32"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="32"/>
+      <c r="I21" s="32"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="32"/>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="27" t="s">
-        <v>279</v>
-      </c>
-      <c r="B22" s="28"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="28"/>
-      <c r="K22" s="28"/>
+      <c r="A22" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="B22" s="29"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="29"/>
+      <c r="E22" s="29"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="29"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="29"/>
+      <c r="K22" s="29"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="29" t="s">
-        <v>279</v>
-      </c>
-      <c r="B23" s="30">
+      <c r="A23" s="30" t="s">
+        <v>280</v>
+      </c>
+      <c r="B23" s="31">
         <v>620.89</v>
       </c>
-      <c r="C23" s="30">
+      <c r="C23" s="31">
         <v>1420.24</v>
       </c>
-      <c r="D23" s="30">
+      <c r="D23" s="31">
         <v>961.12</v>
       </c>
-      <c r="E23" s="30">
+      <c r="E23" s="31">
         <v>1935.78</v>
       </c>
-      <c r="F23" s="30">
+      <c r="F23" s="31">
         <v>761.91</v>
       </c>
-      <c r="G23" s="30">
+      <c r="G23" s="31">
         <v>318.17</v>
       </c>
-      <c r="H23" s="30">
+      <c r="H23" s="31">
         <v>251.61</v>
       </c>
-      <c r="I23" s="31"/>
-      <c r="J23" s="31"/>
-      <c r="K23" s="31"/>
+      <c r="I23" s="32"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="32"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="29" t="s">
-        <v>280</v>
-      </c>
-      <c r="B24" s="30">
+      <c r="A24" s="30" t="s">
+        <v>281</v>
+      </c>
+      <c r="B24" s="31">
         <v>1139.99</v>
       </c>
-      <c r="C24" s="30">
+      <c r="C24" s="31">
         <v>1079.44</v>
       </c>
-      <c r="D24" s="30">
+      <c r="D24" s="31">
         <v>845.72</v>
       </c>
-      <c r="E24" s="31"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="31"/>
-      <c r="I24" s="31"/>
-      <c r="J24" s="31"/>
-      <c r="K24" s="31"/>
+      <c r="E24" s="32"/>
+      <c r="F24" s="32"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="32"/>
+      <c r="I24" s="32"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="32"/>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="27" t="s">
-        <v>281</v>
-      </c>
-      <c r="B25" s="28"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="28"/>
-      <c r="J25" s="28"/>
-      <c r="K25" s="28"/>
+      <c r="A25" s="28" t="s">
+        <v>282</v>
+      </c>
+      <c r="B25" s="29"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="29"/>
+      <c r="E25" s="29"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="29"/>
+      <c r="H25" s="29"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="29"/>
+      <c r="K25" s="29"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="29" t="s">
-        <v>282</v>
-      </c>
-      <c r="B26" s="32">
+      <c r="A26" s="30" t="s">
+        <v>283</v>
+      </c>
+      <c r="B26" s="33">
         <v>4.79</v>
       </c>
-      <c r="C26" s="32">
+      <c r="C26" s="33">
         <v>16.37</v>
       </c>
-      <c r="D26" s="32">
+      <c r="D26" s="33">
         <v>13.14</v>
       </c>
-      <c r="E26" s="32">
+      <c r="E26" s="33">
         <v>26.48</v>
       </c>
-      <c r="F26" s="32">
+      <c r="F26" s="33">
         <v>11.91</v>
       </c>
-      <c r="G26" s="32">
+      <c r="G26" s="33">
         <v>5.51</v>
       </c>
-      <c r="H26" s="32">
+      <c r="H26" s="33">
         <v>4.35</v>
       </c>
-      <c r="I26" s="31"/>
-      <c r="J26" s="31"/>
-      <c r="K26" s="31"/>
+      <c r="I26" s="32"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="32"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="29" t="s">
-        <v>283</v>
-      </c>
-      <c r="B27" s="32">
+      <c r="A27" s="30" t="s">
+        <v>284</v>
+      </c>
+      <c r="B27" s="33">
         <v>14.54</v>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="33">
         <v>14.68</v>
       </c>
-      <c r="D27" s="32">
+      <c r="D27" s="33">
         <v>12.28</v>
       </c>
-      <c r="E27" s="31"/>
-      <c r="F27" s="31"/>
-      <c r="G27" s="31"/>
-      <c r="H27" s="31"/>
-      <c r="I27" s="31"/>
-      <c r="J27" s="31"/>
-      <c r="K27" s="31"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="32"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="32"/>
+      <c r="I27" s="32"/>
+      <c r="J27" s="32"/>
+      <c r="K27" s="32"/>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="27" t="s">
-        <v>284</v>
-      </c>
-      <c r="B28" s="28"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="28"/>
-      <c r="J28" s="28"/>
-      <c r="K28" s="28"/>
+      <c r="A28" s="28" t="s">
+        <v>285</v>
+      </c>
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="29"/>
+      <c r="K28" s="29"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="29" t="s">
-        <v>285</v>
-      </c>
-      <c r="B29" s="33">
+      <c r="A29" s="30" t="s">
+        <v>286</v>
+      </c>
+      <c r="B29" s="34">
         <v>-14.24</v>
       </c>
-      <c r="C29" s="33">
+      <c r="C29" s="34">
         <v>-7.26</v>
       </c>
-      <c r="D29" s="33">
+      <c r="D29" s="34">
         <v>-7.58</v>
       </c>
-      <c r="E29" s="33">
+      <c r="E29" s="34">
         <v>-2.93</v>
       </c>
-      <c r="F29" s="33">
+      <c r="F29" s="34">
         <v>-5.8</v>
       </c>
-      <c r="G29" s="33">
+      <c r="G29" s="34">
         <v>-16.59</v>
       </c>
-      <c r="H29" s="33">
+      <c r="H29" s="34">
         <v>-48.21</v>
       </c>
-      <c r="I29" s="34"/>
-      <c r="J29" s="34"/>
-      <c r="K29" s="34"/>
+      <c r="I29" s="35"/>
+      <c r="J29" s="35"/>
+      <c r="K29" s="35"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="29" t="s">
-        <v>286</v>
-      </c>
-      <c r="B30" s="33">
+      <c r="A30" s="30" t="s">
+        <v>287</v>
+      </c>
+      <c r="B30" s="34">
         <v>-5.96</v>
       </c>
-      <c r="C30" s="33">
+      <c r="C30" s="34">
         <v>-6.22</v>
       </c>
-      <c r="D30" s="33">
+      <c r="D30" s="34">
         <v>-8.92</v>
       </c>
-      <c r="E30" s="34"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="34"/>
-      <c r="H30" s="34"/>
-      <c r="I30" s="34"/>
-      <c r="J30" s="34"/>
-      <c r="K30" s="34"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="35"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="35"/>
+      <c r="I30" s="35"/>
+      <c r="J30" s="35"/>
+      <c r="K30" s="35"/>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="27" t="s">
-        <v>287</v>
-      </c>
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="28"/>
-      <c r="I31" s="28"/>
-      <c r="J31" s="28"/>
-      <c r="K31" s="28"/>
+      <c r="A31" s="28" t="s">
+        <v>288</v>
+      </c>
+      <c r="B31" s="29"/>
+      <c r="C31" s="29"/>
+      <c r="D31" s="29"/>
+      <c r="E31" s="29"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="29"/>
+      <c r="H31" s="29"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="29"/>
+      <c r="K31" s="29"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="29" t="s">
-        <v>288</v>
-      </c>
-      <c r="B32" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="C32" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="D32" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="E32" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="F32" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="G32" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="H32" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="I32" s="34"/>
-      <c r="J32" s="34"/>
-      <c r="K32" s="34"/>
+      <c r="A32" s="30" t="s">
+        <v>289</v>
+      </c>
+      <c r="B32" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="C32" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="D32" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="E32" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="F32" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="G32" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="H32" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="I32" s="35"/>
+      <c r="J32" s="35"/>
+      <c r="K32" s="35"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="29" t="s">
-        <v>289</v>
-      </c>
-      <c r="B33" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="C33" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="D33" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="E33" s="34"/>
-      <c r="F33" s="34"/>
-      <c r="G33" s="34"/>
-      <c r="H33" s="34"/>
-      <c r="I33" s="34"/>
-      <c r="J33" s="34"/>
-      <c r="K33" s="34"/>
+      <c r="A33" s="30" t="s">
+        <v>290</v>
+      </c>
+      <c r="B33" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="C33" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="D33" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="E33" s="35"/>
+      <c r="F33" s="35"/>
+      <c r="G33" s="35"/>
+      <c r="H33" s="35"/>
+      <c r="I33" s="35"/>
+      <c r="J33" s="35"/>
+      <c r="K33" s="35"/>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="29" t="s">
-        <v>290</v>
-      </c>
-      <c r="B34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="C34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="D34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="E34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="F34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="G34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="H34" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="I34" s="34"/>
-      <c r="J34" s="34"/>
-      <c r="K34" s="34"/>
+      <c r="A34" s="30" t="s">
+        <v>291</v>
+      </c>
+      <c r="B34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="C34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="D34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="E34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="F34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="G34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="H34" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="I34" s="35"/>
+      <c r="J34" s="35"/>
+      <c r="K34" s="35"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="29" t="s">
-        <v>291</v>
-      </c>
-      <c r="B35" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="C35" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="D35" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="34"/>
-      <c r="H35" s="34"/>
-      <c r="I35" s="34"/>
-      <c r="J35" s="34"/>
-      <c r="K35" s="34"/>
+      <c r="A35" s="30" t="s">
+        <v>292</v>
+      </c>
+      <c r="B35" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="C35" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="D35" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="E35" s="35"/>
+      <c r="F35" s="35"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="35"/>
+      <c r="I35" s="35"/>
+      <c r="J35" s="35"/>
+      <c r="K35" s="35"/>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="27" t="s">
-        <v>292</v>
-      </c>
-      <c r="B36" s="28"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
-      <c r="F36" s="28"/>
-      <c r="G36" s="28"/>
-      <c r="H36" s="28"/>
-      <c r="I36" s="28"/>
-      <c r="J36" s="28"/>
-      <c r="K36" s="28"/>
+      <c r="A36" s="28" t="s">
+        <v>293</v>
+      </c>
+      <c r="B36" s="29"/>
+      <c r="C36" s="29"/>
+      <c r="D36" s="29"/>
+      <c r="E36" s="29"/>
+      <c r="F36" s="29"/>
+      <c r="G36" s="29"/>
+      <c r="H36" s="29"/>
+      <c r="I36" s="29"/>
+      <c r="J36" s="29"/>
+      <c r="K36" s="29"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="29" t="s">
-        <v>293</v>
-      </c>
-      <c r="B37" s="32">
+      <c r="A37" s="30" t="s">
+        <v>294</v>
+      </c>
+      <c r="B37" s="33">
         <v>2.68</v>
       </c>
-      <c r="C37" s="32">
+      <c r="C37" s="33">
         <v>7.12</v>
       </c>
-      <c r="D37" s="32">
+      <c r="D37" s="33">
         <v>6.38</v>
       </c>
-      <c r="E37" s="32">
+      <c r="E37" s="33">
         <v>9.07</v>
       </c>
-      <c r="F37" s="32">
+      <c r="F37" s="33">
         <v>5.91</v>
       </c>
-      <c r="G37" s="32">
+      <c r="G37" s="33">
         <v>2.48</v>
       </c>
-      <c r="H37" s="32">
+      <c r="H37" s="33">
         <v>1.25</v>
       </c>
-      <c r="I37" s="31"/>
-      <c r="J37" s="31"/>
-      <c r="K37" s="31"/>
+      <c r="I37" s="32"/>
+      <c r="J37" s="32"/>
+      <c r="K37" s="32"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="29" t="s">
-        <v>294</v>
-      </c>
-      <c r="B38" s="32">
+      <c r="A38" s="30" t="s">
+        <v>295</v>
+      </c>
+      <c r="B38" s="33">
         <v>6.56</v>
       </c>
-      <c r="C38" s="32">
+      <c r="C38" s="33">
         <v>6.37</v>
       </c>
-      <c r="D38" s="32">
+      <c r="D38" s="33">
         <v>4.83</v>
       </c>
-      <c r="E38" s="31"/>
-      <c r="F38" s="31"/>
-      <c r="G38" s="31"/>
-      <c r="H38" s="31"/>
-      <c r="I38" s="31"/>
-      <c r="J38" s="31"/>
-      <c r="K38" s="31"/>
+      <c r="E38" s="32"/>
+      <c r="F38" s="32"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="32"/>
+      <c r="I38" s="32"/>
+      <c r="J38" s="32"/>
+      <c r="K38" s="32"/>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="27" t="s">
-        <v>295</v>
-      </c>
-      <c r="B39" s="28"/>
-      <c r="C39" s="28"/>
-      <c r="D39" s="28"/>
-      <c r="E39" s="28"/>
-      <c r="F39" s="28"/>
-      <c r="G39" s="28"/>
-      <c r="H39" s="28"/>
-      <c r="I39" s="28"/>
-      <c r="J39" s="28"/>
-      <c r="K39" s="28"/>
+      <c r="A39" s="28" t="s">
+        <v>296</v>
+      </c>
+      <c r="B39" s="29"/>
+      <c r="C39" s="29"/>
+      <c r="D39" s="29"/>
+      <c r="E39" s="29"/>
+      <c r="F39" s="29"/>
+      <c r="G39" s="29"/>
+      <c r="H39" s="29"/>
+      <c r="I39" s="29"/>
+      <c r="J39" s="29"/>
+      <c r="K39" s="29"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="29" t="s">
-        <v>296</v>
-      </c>
-      <c r="B40" s="32">
+      <c r="A40" s="30" t="s">
+        <v>297</v>
+      </c>
+      <c r="B40" s="33">
         <v>2.8</v>
       </c>
-      <c r="C40" s="32">
+      <c r="C40" s="33">
         <v>7.81</v>
       </c>
-      <c r="D40" s="32">
+      <c r="D40" s="33">
         <v>7.64</v>
       </c>
-      <c r="E40" s="32">
+      <c r="E40" s="33">
         <v>10.75</v>
       </c>
-      <c r="F40" s="32">
+      <c r="F40" s="33">
         <v>8.94</v>
       </c>
-      <c r="G40" s="32">
+      <c r="G40" s="33">
         <v>4.27</v>
       </c>
-      <c r="H40" s="32">
+      <c r="H40" s="33">
         <v>2.0</v>
       </c>
-      <c r="I40" s="31"/>
-      <c r="J40" s="31"/>
-      <c r="K40" s="31"/>
+      <c r="I40" s="32"/>
+      <c r="J40" s="32"/>
+      <c r="K40" s="32"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="29" t="s">
-        <v>297</v>
-      </c>
-      <c r="B41" s="32">
+      <c r="A41" s="30" t="s">
+        <v>298</v>
+      </c>
+      <c r="B41" s="33">
         <v>7.8</v>
       </c>
-      <c r="C41" s="32">
+      <c r="C41" s="33">
         <v>8.25</v>
       </c>
-      <c r="D41" s="32">
+      <c r="D41" s="33">
         <v>6.84</v>
       </c>
-      <c r="E41" s="31"/>
-      <c r="F41" s="31"/>
-      <c r="G41" s="31"/>
-      <c r="H41" s="31"/>
-      <c r="I41" s="31"/>
-      <c r="J41" s="31"/>
-      <c r="K41" s="31"/>
+      <c r="E41" s="32"/>
+      <c r="F41" s="32"/>
+      <c r="G41" s="32"/>
+      <c r="H41" s="32"/>
+      <c r="I41" s="32"/>
+      <c r="J41" s="32"/>
+      <c r="K41" s="32"/>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="27" t="s">
-        <v>298</v>
-      </c>
-      <c r="B42" s="28"/>
-      <c r="C42" s="28"/>
-      <c r="D42" s="28"/>
-      <c r="E42" s="28"/>
-      <c r="F42" s="28"/>
-      <c r="G42" s="28"/>
-      <c r="H42" s="28"/>
-      <c r="I42" s="28"/>
-      <c r="J42" s="28"/>
-      <c r="K42" s="28"/>
+      <c r="A42" s="28" t="s">
+        <v>299</v>
+      </c>
+      <c r="B42" s="29"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="29"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="29"/>
+      <c r="H42" s="29"/>
+      <c r="I42" s="29"/>
+      <c r="J42" s="29"/>
+      <c r="K42" s="29"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="29" t="s">
-        <v>299</v>
-      </c>
-      <c r="B43" s="32">
+      <c r="A43" s="30" t="s">
+        <v>300</v>
+      </c>
+      <c r="B43" s="33">
         <v>52.24</v>
       </c>
-      <c r="C43" s="32">
+      <c r="C43" s="33">
         <v>58.17</v>
       </c>
-      <c r="D43" s="32">
+      <c r="D43" s="33">
         <v>71.91</v>
       </c>
-      <c r="E43" s="30">
+      <c r="E43" s="31">
         <v>175.93</v>
       </c>
-      <c r="F43" s="30">
+      <c r="F43" s="31">
         <v>244.57</v>
       </c>
-      <c r="G43" s="30">
+      <c r="G43" s="31">
         <v>106.48</v>
       </c>
-      <c r="H43" s="30">
+      <c r="H43" s="31">
         <v>182.06</v>
       </c>
-      <c r="I43" s="31"/>
-      <c r="J43" s="31"/>
-      <c r="K43" s="31"/>
+      <c r="I43" s="32"/>
+      <c r="J43" s="32"/>
+      <c r="K43" s="32"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="29" t="s">
-        <v>300</v>
-      </c>
-      <c r="B44" s="32">
+      <c r="A44" s="30" t="s">
+        <v>301</v>
+      </c>
+      <c r="B44" s="33">
         <v>96.27</v>
       </c>
-      <c r="C44" s="30">
+      <c r="C44" s="31">
         <v>102.65</v>
       </c>
-      <c r="D44" s="30">
+      <c r="D44" s="31">
         <v>134.16</v>
       </c>
-      <c r="E44" s="31"/>
-      <c r="F44" s="31"/>
-      <c r="G44" s="31"/>
-      <c r="H44" s="31"/>
-      <c r="I44" s="31"/>
-      <c r="J44" s="31"/>
-      <c r="K44" s="31"/>
+      <c r="E44" s="32"/>
+      <c r="F44" s="32"/>
+      <c r="G44" s="32"/>
+      <c r="H44" s="32"/>
+      <c r="I44" s="32"/>
+      <c r="J44" s="32"/>
+      <c r="K44" s="32"/>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="27" t="s">
-        <v>301</v>
-      </c>
-      <c r="B45" s="28"/>
-      <c r="C45" s="28"/>
-      <c r="D45" s="28"/>
-      <c r="E45" s="28"/>
-      <c r="F45" s="28"/>
-      <c r="G45" s="28"/>
-      <c r="H45" s="28"/>
-      <c r="I45" s="28"/>
-      <c r="J45" s="28"/>
-      <c r="K45" s="28"/>
+      <c r="A45" s="28" t="s">
+        <v>302</v>
+      </c>
+      <c r="B45" s="29"/>
+      <c r="C45" s="29"/>
+      <c r="D45" s="29"/>
+      <c r="E45" s="29"/>
+      <c r="F45" s="29"/>
+      <c r="G45" s="29"/>
+      <c r="H45" s="29"/>
+      <c r="I45" s="29"/>
+      <c r="J45" s="29"/>
+      <c r="K45" s="29"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="29" t="s">
-        <v>302</v>
-      </c>
-      <c r="B46" s="32">
+      <c r="A46" s="30" t="s">
+        <v>303</v>
+      </c>
+      <c r="B46" s="33">
         <v>6.56</v>
       </c>
-      <c r="C46" s="32">
+      <c r="C46" s="33">
         <v>6.37</v>
       </c>
-      <c r="D46" s="32">
+      <c r="D46" s="33">
         <v>4.83</v>
       </c>
-      <c r="E46" s="31"/>
-      <c r="F46" s="31"/>
-      <c r="G46" s="31"/>
-      <c r="H46" s="31"/>
-      <c r="I46" s="31"/>
-      <c r="J46" s="31"/>
-      <c r="K46" s="31"/>
+      <c r="E46" s="32"/>
+      <c r="F46" s="32"/>
+      <c r="G46" s="32"/>
+      <c r="H46" s="32"/>
+      <c r="I46" s="32"/>
+      <c r="J46" s="32"/>
+      <c r="K46" s="32"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="27" t="s">
-        <v>303</v>
-      </c>
-      <c r="B47" s="28"/>
-      <c r="C47" s="28"/>
-      <c r="D47" s="28"/>
-      <c r="E47" s="28"/>
-      <c r="F47" s="28"/>
-      <c r="G47" s="28"/>
-      <c r="H47" s="28"/>
-      <c r="I47" s="28"/>
-      <c r="J47" s="28"/>
-      <c r="K47" s="28"/>
+      <c r="A47" s="28" t="s">
+        <v>304</v>
+      </c>
+      <c r="B47" s="29"/>
+      <c r="C47" s="29"/>
+      <c r="D47" s="29"/>
+      <c r="E47" s="29"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="29"/>
+      <c r="H47" s="29"/>
+      <c r="I47" s="29"/>
+      <c r="J47" s="29"/>
+      <c r="K47" s="29"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="29" t="s">
-        <v>304</v>
-      </c>
-      <c r="B48" s="32">
+      <c r="A48" s="30" t="s">
+        <v>305</v>
+      </c>
+      <c r="B48" s="33">
         <v>48.42</v>
       </c>
-      <c r="C48" s="32">
+      <c r="C48" s="33">
         <v>58.18</v>
       </c>
-      <c r="D48" s="32">
+      <c r="D48" s="33">
         <v>66.02</v>
       </c>
-      <c r="E48" s="30">
+      <c r="E48" s="31">
         <v>177.86</v>
       </c>
-      <c r="F48" s="30">
+      <c r="F48" s="31">
         <v>227.43</v>
       </c>
-      <c r="G48" s="32">
+      <c r="G48" s="33">
         <v>82.95</v>
       </c>
-      <c r="H48" s="30">
+      <c r="H48" s="31">
         <v>120.22</v>
       </c>
-      <c r="I48" s="31"/>
-      <c r="J48" s="31"/>
-      <c r="K48" s="31"/>
+      <c r="I48" s="32"/>
+      <c r="J48" s="32"/>
+      <c r="K48" s="32"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="29" t="s">
-        <v>305</v>
-      </c>
-      <c r="B49" s="32">
+      <c r="A49" s="30" t="s">
+        <v>306</v>
+      </c>
+      <c r="B49" s="33">
         <v>87.6</v>
       </c>
-      <c r="C49" s="32">
+      <c r="C49" s="33">
         <v>94.6</v>
       </c>
-      <c r="D49" s="30">
+      <c r="D49" s="31">
         <v>122.4</v>
       </c>
-      <c r="E49" s="31"/>
-      <c r="F49" s="31"/>
-      <c r="G49" s="31"/>
-      <c r="H49" s="31"/>
-      <c r="I49" s="31"/>
-      <c r="J49" s="31"/>
-      <c r="K49" s="31"/>
+      <c r="E49" s="32"/>
+      <c r="F49" s="32"/>
+      <c r="G49" s="32"/>
+      <c r="H49" s="32"/>
+      <c r="I49" s="32"/>
+      <c r="J49" s="32"/>
+      <c r="K49" s="32"/>
     </row>
     <row r="50" ht="15.75" customHeight="1"/>
     <row r="51" ht="15.75" customHeight="1"/>
